--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -5880,7 +5880,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -5880,7 +5880,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -5880,7 +5880,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -5880,7 +5880,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -5880,7 +5880,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -5880,7 +5880,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -5880,7 +5880,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -5880,7 +5880,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -5880,7 +5880,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -5880,7 +5880,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -5880,7 +5880,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -5880,7 +5880,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -5880,7 +5880,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -5880,7 +5880,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260614_210109.xlsx
@@ -5880,7 +5880,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
